--- a/docs/Mapping_casi_uso/cittadinanza/Citt_048.xlsx
+++ b/docs/Mapping_casi_uso/cittadinanza/Citt_048.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="58">
   <si>
     <t>Sezione</t>
   </si>
@@ -144,6 +144,39 @@
   </si>
   <si>
     <t>tipologia</t>
+  </si>
+  <si>
+    <t>Atto collegato di Cittadinanza</t>
+  </si>
+  <si>
+    <t>evento.eventoCollegatoCittadinanza</t>
+  </si>
+  <si>
+    <t>opzionale</t>
+  </si>
+  <si>
+    <t>Tipo evento</t>
+  </si>
+  <si>
+    <t>idtipocontenuto</t>
+  </si>
+  <si>
+    <t>Parte</t>
+  </si>
+  <si>
+    <t>parte</t>
+  </si>
+  <si>
+    <t>Serie</t>
+  </si>
+  <si>
+    <t>serie</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>volume</t>
   </si>
   <si>
     <t>Correzione</t>
@@ -211,10 +244,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="20.203125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.4296875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="33.30859375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.5625" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="33.921875" customWidth="true" bestFit="true"/>
@@ -619,21 +652,320 @@
         <v>44</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" s="2" t="s">
+      <c r="E31" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" s="2" t="s">
         <v>19</v>
       </c>
     </row>
